--- a/files/Running_Belt_GTM_Master_Tracker_UPDATED.xlsx
+++ b/files/Running_Belt_GTM_Master_Tracker_UPDATED.xlsx
@@ -741,7 +741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="36" min="1" max="1"/>
@@ -1643,60 +1643,132 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="36" t="inlineStr">
         <is>
           <t>P21: Visual Brand Board (colors, fonts, voice, photography)</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" t="inlineStr">
+      <c r="D26" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="36" t="inlineStr">
         <is>
           <t>Complete (100%)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="36" t="inlineStr">
         <is>
           <t>P22: Annual Operations Calendar (12-month recurring tasks)</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" t="inlineStr">
+      <c r="D27" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="36" t="inlineStr">
         <is>
           <t>Complete (100%)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="36" t="inlineStr">
+        <is>
+          <t>P23: Social Media Content Calendar (30-day)</t>
+        </is>
+      </c>
+      <c r="D28" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="36" t="inlineStr">
+        <is>
+          <t>Complete (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="36" t="inlineStr">
+        <is>
+          <t>P24: Founder Video Script Pack (5 scripts)</t>
+        </is>
+      </c>
+      <c r="D29" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="36" t="inlineStr">
+        <is>
+          <t>Complete (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="36" t="inlineStr">
+        <is>
+          <t>P25: Amazon PPC Keyword Research (30 keywords + negatives)</t>
+        </is>
+      </c>
+      <c r="D30" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="36" t="inlineStr">
+        <is>
+          <t>Complete (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P26: Investor Pitch Deck (10-slide PPTX)</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Complete (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>22 projects</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>69 deliverables</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>285 tasks + 10 execution/operational tools = COMPLETE</t>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>26 projects</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>73 deliverables</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>285 tasks + 14 execution tools = COMPLETE</t>
         </is>
       </c>
     </row>
